--- a/datos_excel/dim_eventos.xlsx
+++ b/datos_excel/dim_eventos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>nombre_evento</t>
   </si>
@@ -37,85 +37,112 @@
     <t>categorias_impactadas</t>
   </si>
   <si>
-    <t>dia_sin_iva_1</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_2</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_3</t>
-  </si>
-  <si>
-    <t>dia_madre_2022</t>
-  </si>
-  <si>
-    <t>amor_amistad_2022</t>
-  </si>
-  <si>
-    <t>navidad_2022</t>
-  </si>
-  <si>
-    <t>carnaval_baq_2022</t>
-  </si>
-  <si>
-    <t>feria_cali_2022</t>
-  </si>
-  <si>
-    <t>black_friday_2022</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_4</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_5</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_6</t>
-  </si>
-  <si>
-    <t>dia_madre_2023</t>
-  </si>
-  <si>
-    <t>amor_amistad_2023</t>
-  </si>
-  <si>
-    <t>navidad_2023</t>
-  </si>
-  <si>
-    <t>carnaval_baq_2023</t>
-  </si>
-  <si>
-    <t>feria_cali_2023</t>
-  </si>
-  <si>
-    <t>black_friday_2023</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_7</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_8</t>
-  </si>
-  <si>
-    <t>dia_sin_iva_9</t>
-  </si>
-  <si>
-    <t>dia_madre_2024</t>
-  </si>
-  <si>
-    <t>amor_amistad_2024</t>
-  </si>
-  <si>
-    <t>navidad_2024</t>
-  </si>
-  <si>
-    <t>carnaval_baq_2024</t>
-  </si>
-  <si>
-    <t>feria_cali_2024</t>
-  </si>
-  <si>
-    <t>black_friday_2024</t>
+    <t>dia_sin_iva_mar22</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_jun22</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_oct22</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_mar23</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_jun23</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_oct23</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_mar24</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_jun24</t>
+  </si>
+  <si>
+    <t>dia_sin_iva_oct24</t>
+  </si>
+  <si>
+    <t>dia_madre_22</t>
+  </si>
+  <si>
+    <t>dia_madre_23</t>
+  </si>
+  <si>
+    <t>dia_madre_24</t>
+  </si>
+  <si>
+    <t>amor_amistad_22</t>
+  </si>
+  <si>
+    <t>amor_amistad_23</t>
+  </si>
+  <si>
+    <t>amor_amistad_24</t>
+  </si>
+  <si>
+    <t>navidad_22</t>
+  </si>
+  <si>
+    <t>navidad_23</t>
+  </si>
+  <si>
+    <t>navidad_24</t>
+  </si>
+  <si>
+    <t>black_friday_22</t>
+  </si>
+  <si>
+    <t>black_friday_23</t>
+  </si>
+  <si>
+    <t>black_friday_24</t>
+  </si>
+  <si>
+    <t>carnaval_22</t>
+  </si>
+  <si>
+    <t>carnaval_23</t>
+  </si>
+  <si>
+    <t>carnaval_24</t>
+  </si>
+  <si>
+    <t>feria_cali_22</t>
+  </si>
+  <si>
+    <t>feria_cali_23</t>
+  </si>
+  <si>
+    <t>feria_cali_24</t>
+  </si>
+  <si>
+    <t>flores_med_22</t>
+  </si>
+  <si>
+    <t>flores_med_23</t>
+  </si>
+  <si>
+    <t>flores_med_24</t>
+  </si>
+  <si>
+    <t>regreso_ene22</t>
+  </si>
+  <si>
+    <t>regreso_jul22</t>
+  </si>
+  <si>
+    <t>regreso_ene23</t>
+  </si>
+  <si>
+    <t>regreso_jul23</t>
+  </si>
+  <si>
+    <t>regreso_ene24</t>
+  </si>
+  <si>
+    <t>regreso_jul24</t>
   </si>
   <si>
     <t>2022-03-11</t>
@@ -127,76 +154,103 @@
     <t>2022-10-28</t>
   </si>
   <si>
+    <t>2023-03-03</t>
+  </si>
+  <si>
+    <t>2023-06-16</t>
+  </si>
+  <si>
+    <t>2023-10-27</t>
+  </si>
+  <si>
+    <t>2024-03-08</t>
+  </si>
+  <si>
+    <t>2024-06-14</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
     <t>2022-05-08</t>
   </si>
   <si>
+    <t>2023-05-14</t>
+  </si>
+  <si>
+    <t>2024-05-12</t>
+  </si>
+  <si>
     <t>2022-09-17</t>
   </si>
   <si>
+    <t>2023-09-16</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
     <t>2022-12-18</t>
   </si>
   <si>
+    <t>2023-12-17</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2022-11-25</t>
+  </si>
+  <si>
+    <t>2023-11-24</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
     <t>2022-02-28</t>
   </si>
   <si>
+    <t>2023-02-20</t>
+  </si>
+  <si>
+    <t>2024-02-10</t>
+  </si>
+  <si>
     <t>2022-12-26</t>
   </si>
   <si>
-    <t>2022-11-25</t>
-  </si>
-  <si>
-    <t>2023-03-03</t>
-  </si>
-  <si>
-    <t>2023-06-16</t>
-  </si>
-  <si>
-    <t>2023-10-27</t>
-  </si>
-  <si>
-    <t>2023-05-14</t>
-  </si>
-  <si>
-    <t>2023-09-16</t>
-  </si>
-  <si>
-    <t>2023-12-17</t>
-  </si>
-  <si>
-    <t>2023-02-20</t>
-  </si>
-  <si>
     <t>2023-12-26</t>
   </si>
   <si>
-    <t>2023-11-24</t>
-  </si>
-  <si>
-    <t>2024-03-08</t>
-  </si>
-  <si>
-    <t>2024-06-14</t>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-  </si>
-  <si>
-    <t>2024-05-12</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-02-10</t>
-  </si>
-  <si>
     <t>2024-12-26</t>
   </si>
   <si>
-    <t>2024-11-29</t>
+    <t>2022-08-01</t>
+  </si>
+  <si>
+    <t>2023-08-07</t>
+  </si>
+  <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
+    <t>2022-01-24</t>
+  </si>
+  <si>
+    <t>2022-07-18</t>
+  </si>
+  <si>
+    <t>2023-01-23</t>
+  </si>
+  <si>
+    <t>2023-07-17</t>
+  </si>
+  <si>
+    <t>2024-01-22</t>
+  </si>
+  <si>
+    <t>2024-07-15</t>
   </si>
   <si>
     <t>nacional</t>
@@ -206,6 +260,9 @@
   </si>
   <si>
     <t>Cali</t>
+  </si>
+  <si>
+    <t>Medellín</t>
   </si>
   <si>
     <t>TODAS</t>
@@ -543,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -574,22 +631,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -597,22 +654,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -620,22 +677,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -643,22 +700,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -666,22 +723,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -689,22 +746,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -712,22 +769,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -735,22 +792,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -758,22 +815,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -781,22 +838,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -804,22 +861,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -827,22 +884,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -850,22 +907,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -873,10 +930,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -885,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -896,22 +953,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -919,22 +976,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -942,22 +999,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -965,22 +1022,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -988,22 +1045,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1011,22 +1068,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1034,22 +1091,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1057,22 +1114,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1080,10 +1137,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1092,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1103,22 +1160,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1126,22 +1183,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1149,10 +1206,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1161,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1172,22 +1229,229 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>40</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>40</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>40</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>25</v>
+      </c>
+      <c r="G33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
